--- a/storage/app/public/templates/excel-confirmacion/EXCEL_DE_CONFIRMACION_GENERAL.xlsx
+++ b/storage/app/public/templates/excel-confirmacion/EXCEL_DE_CONFIRMACION_GENERAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Proyectos\Probusiness\intranet_back\public\storage\templates\excel-confirmacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3CC81B-A7E4-407A-B7AB-7BB1E81B66E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB2AFBB-3A58-4B3D-A558-2674CD4E854C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>IMPORTANTE CONFIRMAR LO SIGUIENTES DATOS</t>
   </si>
@@ -89,24 +89,6 @@
     <t>CARACTERISTICAS</t>
   </si>
   <si>
-    <t>NOMBRE COMPLETO:</t>
-  </si>
-  <si>
-    <t>RAZON SOCIAL:</t>
-  </si>
-  <si>
-    <t>RUC:</t>
-  </si>
-  <si>
-    <t>FACTURA O BOLETA:</t>
-  </si>
-  <si>
-    <t>1-. CONFIRMACION DE DATOS DEL CLIENTE:</t>
-  </si>
-  <si>
-    <t>2-.  INFORMACIÓN DE LA FACTURA:</t>
-  </si>
-  <si>
     <t>PRECIO EXW</t>
   </si>
   <si>
@@ -125,10 +107,10 @@
     <t>N.º</t>
   </si>
   <si>
-    <t>DNI/CARNET DE EXTRANJERIA:</t>
-  </si>
-  <si>
     <t>GENERAL</t>
+  </si>
+  <si>
+    <t>1-.  INFORMACIÓN DE LA FACTURA:</t>
   </si>
 </sst>
 </file>
@@ -218,7 +200,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -303,166 +285,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -470,7 +298,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -496,10 +324,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -522,6 +346,74 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -529,118 +421,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -665,6 +445,60 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>845373</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>66077</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>708213</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>169881</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{157D4141-C7A0-41E7-9413-1D8F105FB747}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect t="38991" b="39110"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5175326" y="639818"/>
+          <a:ext cx="5223734" cy="820981"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
@@ -970,154 +804,148 @@
     </row>
     <row r="2" spans="1:67" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="42"/>
-    </row>
-    <row r="3" spans="1:67" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="27"/>
+    </row>
+    <row r="3" spans="1:67" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
     </row>
     <row r="4" spans="1:67" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
-      <c r="B4" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="51"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
       <c r="BM4"/>
       <c r="BN4"/>
       <c r="BO4"/>
     </row>
     <row r="5" spans="1:67" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
-      <c r="B5" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="29"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
       <c r="BM5"/>
       <c r="BN5"/>
       <c r="BO5"/>
     </row>
     <row r="6" spans="1:67" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
-      <c r="B6" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="29"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
       <c r="BM6"/>
       <c r="BN6"/>
       <c r="BO6"/>
     </row>
     <row r="7" spans="1:67" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
-      <c r="B7" s="36" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="29"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
     </row>
     <row r="8" spans="1:67" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
-      <c r="B8" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="37"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="29"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-    </row>
-    <row r="9" spans="1:67" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+    </row>
+    <row r="9" spans="1:67" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
-      <c r="B9" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="44"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
     </row>
     <row r="10" spans="1:67" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
     </row>
     <row r="11" spans="1:67" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
-      <c r="B11" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="34"/>
-      <c r="D11" s="35"/>
+      <c r="B11" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="20"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
@@ -1142,38 +970,38 @@
       <c r="L12" s="7"/>
     </row>
     <row r="13" spans="1:67" s="5" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="14" t="s">
+      <c r="A13" s="10"/>
+      <c r="B13" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D13" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="14" t="s">
+      <c r="D13" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F13" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="14" t="s">
+      <c r="F13" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I13" s="15" t="s">
+      <c r="H13" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="L13" s="14" t="s">
+      <c r="J13" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="L13" s="13" t="s">
         <v>4</v>
       </c>
       <c r="M13" s="4"/>
@@ -1233,199 +1061,199 @@
       <c r="BO13" s="4"/>
     </row>
     <row r="14" spans="1:67" x14ac:dyDescent="0.3">
-      <c r="A14" s="30" t="str">
+      <c r="A14" s="17" t="str">
         <f>+UPPER($E$5)</f>
         <v/>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="28">
         <v>1</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="21"/>
-      <c r="H14" s="23">
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="30"/>
+      <c r="H14" s="32">
         <v>0</v>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="34">
         <f>G14*H14</f>
         <v>0</v>
       </c>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="20"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="36"/>
     </row>
     <row r="15" spans="1:67" x14ac:dyDescent="0.3">
-      <c r="A15" s="30"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="20"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="36"/>
     </row>
     <row r="16" spans="1:67" x14ac:dyDescent="0.3">
-      <c r="A16" s="30"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="20"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="36"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="30"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="20"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="36"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="30"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="27"/>
-      <c r="L18" s="20"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="36"/>
     </row>
     <row r="19" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="30"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="20"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="36"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="30"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="20"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="36"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="30"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="20"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="36"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="30"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="20"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="36"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="30"/>
-      <c r="B23" s="32"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="20"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="36"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="30"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="20"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="36"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="30"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="20"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="36"/>
     </row>
     <row r="26" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A26" s="6"/>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="17">
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="16">
         <f>SUM(G14:G25)</f>
         <v>0</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="15">
         <f>SUM(I14:I25)</f>
         <v>0</v>
       </c>
@@ -1435,14 +1263,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" selectLockedCells="1" sort="0"/>
-  <mergeCells count="26">
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="H4:L9"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B26:F26"/>
+  <mergeCells count="15">
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="C14:C25"/>
     <mergeCell ref="B14:B25"/>
@@ -1453,18 +1274,15 @@
     <mergeCell ref="F14:F25"/>
     <mergeCell ref="K14:K25"/>
     <mergeCell ref="J14:J25"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="A14:A25"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="D14:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B3:L10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>